--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.17298100549307</v>
+        <v>4.903109413392624</v>
       </c>
       <c r="D2" t="n">
-        <v>30.83022959744363</v>
+        <v>5.00991230958459</v>
       </c>
       <c r="E2" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F2" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.41933101468013</v>
+        <v>4.943141289885522</v>
       </c>
       <c r="D3" t="n">
-        <v>30.76791230486016</v>
+        <v>4.999785749539776</v>
       </c>
       <c r="E3" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F3" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.43020565605949</v>
+        <v>5.594908419109668</v>
       </c>
       <c r="D4" t="n">
-        <v>34.73249831745019</v>
+        <v>5.644030976585657</v>
       </c>
       <c r="E4" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F4" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.33427197794646</v>
+        <v>2.166819196416299</v>
       </c>
       <c r="D5" t="n">
-        <v>13.96054223113164</v>
+        <v>2.268588112558891</v>
       </c>
       <c r="E5" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F5" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54823707952798</v>
+        <v>2.689088525423296</v>
       </c>
       <c r="D6" t="n">
-        <v>17.08129388586392</v>
+        <v>2.775710256452887</v>
       </c>
       <c r="E6" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F6" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.36616565696163</v>
+        <v>3.309501919256265</v>
       </c>
       <c r="D7" t="n">
-        <v>20.51623143482389</v>
+        <v>3.333887608158882</v>
       </c>
       <c r="E7" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F7" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.16750078497977</v>
+        <v>6.202218877559213</v>
       </c>
       <c r="D8" t="n">
-        <v>38.10176881911396</v>
+        <v>6.191537433106018</v>
       </c>
       <c r="E8" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F8" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.80838947004778</v>
+        <v>3.543863288882765</v>
       </c>
       <c r="D9" t="n">
-        <v>21.60005526351713</v>
+        <v>3.510008980321533</v>
       </c>
       <c r="E9" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F9" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.3105192698518</v>
+        <v>5.412959381350918</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02374555083002</v>
+        <v>5.366358652009879</v>
       </c>
       <c r="E10" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F10" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.83738248227687</v>
+        <v>3.873574653369991</v>
       </c>
       <c r="D11" t="n">
-        <v>23.21686501374575</v>
+        <v>3.772740564733685</v>
       </c>
       <c r="E11" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F11" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.97228025766635</v>
+        <v>5.195495541870782</v>
       </c>
       <c r="D12" t="n">
-        <v>31.43886964318016</v>
+        <v>5.108816317016776</v>
       </c>
       <c r="E12" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F12" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.6484924382712</v>
+        <v>4.817880021219071</v>
       </c>
       <c r="D13" t="n">
-        <v>28.98905880926663</v>
+        <v>4.710722056505827</v>
       </c>
       <c r="E13" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F13" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.901228927864413</v>
+        <v>1.283949700777967</v>
       </c>
       <c r="D14" t="n">
-        <v>5.711283334571584</v>
+        <v>0.9280835418678823</v>
       </c>
       <c r="E14" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F14" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.684955709108177</v>
+        <v>1.411305302730079</v>
       </c>
       <c r="D15" t="n">
-        <v>11.61870980415127</v>
+        <v>1.888040343174582</v>
       </c>
       <c r="E15" t="n">
-        <v>9.450995590013695</v>
+        <v>1.535786783377225</v>
       </c>
       <c r="F15" t="n">
-        <v>9.338360516850525</v>
+        <v>1.51748358398821</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
